--- a/static/data/exports/Retro_PY_GE_2009.xlsx
+++ b/static/data/exports/Retro_PY_GE_2009.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -17158,7 +17158,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18658,7 +18658,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19858,7 +19858,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20758,7 +20758,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -21208,7 +21208,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21658,7 +21658,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21883,7 +21883,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -22258,7 +22258,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -23308,7 +23308,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23983,7 +23983,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24808,7 +24808,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25708,7 +25708,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25783,7 +25783,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -26233,7 +26233,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26458,7 +26458,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26533,7 +26533,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26833,7 +26833,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26983,7 +26983,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -27058,7 +27058,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -27208,7 +27208,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -27358,7 +27358,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -27433,7 +27433,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27583,7 +27583,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -27658,7 +27658,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -27883,7 +27883,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -28183,7 +28183,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -28408,7 +28408,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28558,7 +28558,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28783,7 +28783,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P378" t="n">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -28933,7 +28933,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -29008,7 +29008,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P384" t="n">
@@ -29308,7 +29308,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -29383,7 +29383,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P386" t="n">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29533,7 +29533,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P389" t="n">
@@ -29683,7 +29683,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29758,7 +29758,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P392" t="n">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -30058,7 +30058,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P397" t="n">
@@ -30283,7 +30283,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -30358,7 +30358,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P400" t="n">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -30583,7 +30583,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30658,7 +30658,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30733,7 +30733,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30808,7 +30808,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -30883,7 +30883,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -31033,7 +31033,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P408" t="n">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -31183,7 +31183,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -31258,7 +31258,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -31333,7 +31333,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -31408,7 +31408,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P413" t="n">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -31558,7 +31558,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31633,7 +31633,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31708,7 +31708,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -32008,7 +32008,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P422" t="n">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -32233,7 +32233,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -32308,7 +32308,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P425" t="n">
@@ -32383,7 +32383,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -32458,7 +32458,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -32533,7 +32533,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P428" t="n">
@@ -32608,7 +32608,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P429" t="n">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32833,7 +32833,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P433" t="n">
@@ -32983,7 +32983,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -33133,7 +33133,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P436" t="n">
@@ -33208,7 +33208,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P438" t="n">
@@ -33358,7 +33358,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -33433,7 +33433,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -33508,7 +33508,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33658,7 +33658,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P443" t="n">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P444" t="n">
@@ -33808,7 +33808,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P445" t="n">
@@ -33883,7 +33883,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33958,7 +33958,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -34183,7 +34183,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -34258,7 +34258,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P451" t="n">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P452" t="n">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -34483,7 +34483,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P454" t="n">
@@ -34558,7 +34558,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -34633,7 +34633,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P458" t="n">
@@ -34858,7 +34858,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P460" t="n">
@@ -35008,7 +35008,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -35158,7 +35158,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -35233,7 +35233,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -35308,7 +35308,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P465" t="n">
@@ -35383,7 +35383,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P467" t="n">
@@ -35533,7 +35533,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -35608,7 +35608,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35683,7 +35683,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35758,7 +35758,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35833,7 +35833,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P472" t="n">
@@ -35908,7 +35908,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P473" t="n">
@@ -35983,7 +35983,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -36058,7 +36058,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P475" t="n">
@@ -36133,7 +36133,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -36208,7 +36208,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -36283,7 +36283,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -36358,7 +36358,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -36508,7 +36508,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P481" t="n">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -36658,7 +36658,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P484" t="n">
@@ -36808,7 +36808,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -37033,7 +37033,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P488" t="n">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P489" t="n">
@@ -37183,7 +37183,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -37258,7 +37258,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P491" t="n">
@@ -37333,7 +37333,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P492" t="n">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -37483,7 +37483,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -37558,7 +37558,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P495" t="n">
@@ -37633,7 +37633,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37708,7 +37708,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37783,7 +37783,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37858,7 +37858,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -37933,7 +37933,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P500" t="n">
@@ -38008,7 +38008,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P502" t="n">
@@ -38158,7 +38158,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -38233,7 +38233,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -38383,7 +38383,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P506" t="n">
@@ -38458,7 +38458,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P507" t="n">
@@ -38533,7 +38533,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P508" t="n">
@@ -38608,7 +38608,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P509" t="n">
@@ -38683,7 +38683,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P510" t="n">
@@ -38758,7 +38758,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38833,7 +38833,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
@@ -38908,7 +38908,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P513" t="n">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -39058,7 +39058,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P516" t="n">
@@ -39208,7 +39208,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P518" t="n">
@@ -39358,7 +39358,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P519" t="n">
@@ -39433,7 +39433,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P520" t="n">
@@ -39508,7 +39508,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -39583,7 +39583,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -39658,7 +39658,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P523" t="n">
@@ -39733,7 +39733,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39808,7 +39808,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P525" t="n">
@@ -39883,7 +39883,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39958,7 +39958,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -40033,7 +40033,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -40108,7 +40108,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P529" t="n">
@@ -40183,7 +40183,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -40258,7 +40258,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P531" t="n">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -40408,7 +40408,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P533" t="n">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -40558,7 +40558,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P535" t="n">
@@ -40633,7 +40633,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40708,7 +40708,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P537" t="n">
@@ -40783,7 +40783,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40858,7 +40858,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40933,7 +40933,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -41008,7 +41008,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -41083,7 +41083,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P542" t="n">
@@ -41158,7 +41158,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -41233,7 +41233,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P544" t="n">
@@ -41308,7 +41308,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P545" t="n">
@@ -41383,7 +41383,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P546" t="n">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -41533,7 +41533,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -41608,7 +41608,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -41683,7 +41683,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41758,7 +41758,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41833,7 +41833,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P552" t="n">
@@ -41908,7 +41908,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41983,7 +41983,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -42058,7 +42058,7 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P555" t="n">
@@ -42133,7 +42133,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P556" t="n">
@@ -42208,7 +42208,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -42283,7 +42283,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -42358,7 +42358,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -42433,7 +42433,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P560" t="n">
@@ -42508,7 +42508,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P561" t="n">
@@ -42583,7 +42583,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P562" t="n">
@@ -42658,7 +42658,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P563" t="n">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42808,7 +42808,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42883,7 +42883,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42958,7 +42958,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P567" t="n">
@@ -43033,7 +43033,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -43183,7 +43183,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -43258,7 +43258,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P571" t="n">
@@ -43333,7 +43333,7 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P572" t="n">
@@ -43408,7 +43408,7 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P573" t="n">
@@ -43483,7 +43483,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P574" t="n">
@@ -43558,7 +43558,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P575" t="n">
@@ -43633,7 +43633,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P576" t="n">
@@ -43708,7 +43708,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P577" t="n">
@@ -43783,7 +43783,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P578" t="n">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P579" t="n">
@@ -43933,7 +43933,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P580" t="n">
@@ -44008,7 +44008,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P581" t="n">
@@ -44083,7 +44083,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P582" t="n">
@@ -44158,7 +44158,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P583" t="n">
@@ -44233,7 +44233,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P584" t="n">
@@ -44308,7 +44308,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P585" t="n">
@@ -44383,7 +44383,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P586" t="n">
@@ -44458,7 +44458,7 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P587" t="n">
@@ -44533,7 +44533,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P588" t="n">
@@ -44608,7 +44608,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P589" t="n">
@@ -44683,7 +44683,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P590" t="n">
@@ -44758,7 +44758,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P591" t="n">
@@ -44833,7 +44833,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P592" t="n">
@@ -44908,7 +44908,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P593" t="n">
@@ -44983,7 +44983,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P594" t="n">
@@ -45058,7 +45058,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P595" t="n">
@@ -45133,7 +45133,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P596" t="n">
@@ -45208,7 +45208,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P597" t="n">
@@ -45283,7 +45283,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P598" t="n">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -45433,7 +45433,7 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P600" t="n">
@@ -45508,7 +45508,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P601" t="n">
@@ -45583,7 +45583,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P602" t="n">
@@ -45658,7 +45658,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P603" t="n">
@@ -45733,7 +45733,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P604" t="n">
@@ -45808,7 +45808,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P605" t="n">
@@ -45883,7 +45883,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P606" t="n">
@@ -45958,7 +45958,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P607" t="n">
@@ -46033,7 +46033,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P608" t="n">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P609" t="n">
@@ -46183,7 +46183,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P610" t="n">
@@ -46258,7 +46258,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P611" t="n">
@@ -46333,7 +46333,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P612" t="n">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P613" t="n">
@@ -46483,7 +46483,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P614" t="n">
@@ -46558,7 +46558,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P615" t="n">
@@ -46633,7 +46633,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P616" t="n">
@@ -46708,7 +46708,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P617" t="n">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P618" t="n">
@@ -46858,7 +46858,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P619" t="n">
@@ -46933,7 +46933,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P620" t="n">
@@ -47008,7 +47008,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P621" t="n">
@@ -47083,7 +47083,7 @@
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P622" t="n">
@@ -47158,7 +47158,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P623" t="n">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P624" t="n">
@@ -47308,7 +47308,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P625" t="n">
@@ -47383,7 +47383,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P626" t="n">
@@ -47458,7 +47458,7 @@
       </c>
       <c r="O627" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P627" t="n">
@@ -47533,7 +47533,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P628" t="n">
@@ -47608,7 +47608,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P629" t="n">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P630" t="n">
@@ -47758,7 +47758,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P631" t="n">
@@ -47833,7 +47833,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P632" t="n">
@@ -47908,7 +47908,7 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P633" t="n">
@@ -47983,7 +47983,7 @@
       </c>
       <c r="O634" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P634" t="n">
@@ -48058,7 +48058,7 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P635" t="n">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P636" t="n">
@@ -48208,7 +48208,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P637" t="n">
@@ -48283,7 +48283,7 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P638" t="n">
@@ -48358,7 +48358,7 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P639" t="n">
@@ -48433,7 +48433,7 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P640" t="n">
@@ -48508,7 +48508,7 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P641" t="n">
@@ -48583,7 +48583,7 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P642" t="n">
@@ -48658,7 +48658,7 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P643" t="n">
@@ -48733,7 +48733,7 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P644" t="n">
@@ -48808,7 +48808,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P645" t="n">
@@ -48883,7 +48883,7 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P646" t="n">
@@ -48958,7 +48958,7 @@
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P647" t="n">
@@ -49033,7 +49033,7 @@
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P648" t="n">
@@ -49108,7 +49108,7 @@
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P649" t="n">
@@ -49183,7 +49183,7 @@
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P650" t="n">
@@ -49258,7 +49258,7 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P651" t="n">
@@ -49333,7 +49333,7 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P652" t="n">
@@ -49408,7 +49408,7 @@
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P653" t="n">
@@ -49483,7 +49483,7 @@
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P654" t="n">
@@ -49558,7 +49558,7 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P655" t="n">
@@ -49633,7 +49633,7 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P656" t="n">
@@ -49708,7 +49708,7 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P657" t="n">
@@ -49783,7 +49783,7 @@
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P658" t="n">
@@ -49858,7 +49858,7 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P659" t="n">
@@ -49933,7 +49933,7 @@
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P660" t="n">
@@ -50008,7 +50008,7 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P661" t="n">
@@ -50083,7 +50083,7 @@
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P662" t="n">
@@ -50158,7 +50158,7 @@
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P663" t="n">
@@ -50233,7 +50233,7 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P664" t="n">
@@ -50308,7 +50308,7 @@
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P665" t="n">
@@ -50383,7 +50383,7 @@
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P666" t="n">
@@ -50458,7 +50458,7 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P667" t="n">
@@ -50533,7 +50533,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P668" t="n">
@@ -50608,7 +50608,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -50683,7 +50683,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P670" t="n">
@@ -50758,7 +50758,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -50833,7 +50833,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P673" t="n">
@@ -50983,7 +50983,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P674" t="n">
@@ -51058,7 +51058,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -51133,7 +51133,7 @@
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P676" t="n">
@@ -51208,7 +51208,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P677" t="n">
@@ -51283,7 +51283,7 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P678" t="n">
@@ -51358,7 +51358,7 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P679" t="n">
@@ -51433,7 +51433,7 @@
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P680" t="n">
@@ -51508,7 +51508,7 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P681" t="n">
@@ -51583,7 +51583,7 @@
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P682" t="n">
@@ -51658,7 +51658,7 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P683" t="n">
@@ -51733,7 +51733,7 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P684" t="n">
@@ -51808,7 +51808,7 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P685" t="n">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P686" t="n">
@@ -51958,7 +51958,7 @@
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P687" t="n">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P688" t="n">
@@ -52108,7 +52108,7 @@
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P689" t="n">
@@ -52183,7 +52183,7 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P690" t="n">
@@ -52258,7 +52258,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P691" t="n">
@@ -52333,7 +52333,7 @@
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P692" t="n">
@@ -52408,7 +52408,7 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P693" t="n">
@@ -52483,7 +52483,7 @@
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P694" t="n">
@@ -52558,7 +52558,7 @@
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P695" t="n">
@@ -52633,7 +52633,7 @@
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P696" t="n">
@@ -52708,7 +52708,7 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P697" t="n">
@@ -52783,7 +52783,7 @@
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P698" t="n">
@@ -52858,7 +52858,7 @@
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P699" t="n">
@@ -52933,7 +52933,7 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P700" t="n">
@@ -53008,7 +53008,7 @@
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P701" t="n">
@@ -53083,7 +53083,7 @@
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P702" t="n">
@@ -53158,7 +53158,7 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P703" t="n">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P704" t="n">
@@ -53308,7 +53308,7 @@
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P705" t="n">
@@ -53383,7 +53383,7 @@
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P706" t="n">
@@ -53458,7 +53458,7 @@
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P707" t="n">
@@ -53533,7 +53533,7 @@
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P708" t="n">
@@ -53608,7 +53608,7 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P709" t="n">
@@ -53683,7 +53683,7 @@
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P710" t="n">
@@ -53758,7 +53758,7 @@
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P711" t="n">
@@ -53833,7 +53833,7 @@
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P712" t="n">
@@ -53908,7 +53908,7 @@
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P713" t="n">
@@ -53983,7 +53983,7 @@
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P714" t="n">
@@ -54058,7 +54058,7 @@
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P715" t="n">
@@ -54133,7 +54133,7 @@
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P716" t="n">
@@ -54208,7 +54208,7 @@
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P717" t="n">
@@ -54283,7 +54283,7 @@
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P718" t="n">
@@ -54358,7 +54358,7 @@
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P719" t="n">
@@ -54433,7 +54433,7 @@
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P720" t="n">
@@ -54508,7 +54508,7 @@
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P721" t="n">
@@ -54583,7 +54583,7 @@
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P722" t="n">
@@ -54658,7 +54658,7 @@
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P723" t="n">
@@ -54733,7 +54733,7 @@
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P724" t="n">
@@ -54808,7 +54808,7 @@
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P725" t="n">
@@ -54883,7 +54883,7 @@
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P726" t="n">
@@ -54958,7 +54958,7 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P727" t="n">
@@ -55033,7 +55033,7 @@
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P728" t="n">
@@ -55108,7 +55108,7 @@
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P729" t="n">
@@ -55183,7 +55183,7 @@
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P730" t="n">
@@ -55258,7 +55258,7 @@
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P731" t="n">
@@ -55333,7 +55333,7 @@
       </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P732" t="n">
@@ -55408,7 +55408,7 @@
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P733" t="n">
@@ -55483,7 +55483,7 @@
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P734" t="n">
@@ -55558,7 +55558,7 @@
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P735" t="n">
@@ -55633,7 +55633,7 @@
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P736" t="n">
@@ -55708,7 +55708,7 @@
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P737" t="n">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P738" t="n">
@@ -55858,7 +55858,7 @@
       </c>
       <c r="O739" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P739" t="n">
@@ -55933,7 +55933,7 @@
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P740" t="n">
@@ -56008,7 +56008,7 @@
       </c>
       <c r="O741" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P741" t="n">
@@ -56083,7 +56083,7 @@
       </c>
       <c r="O742" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P742" t="n">
@@ -56158,7 +56158,7 @@
       </c>
       <c r="O743" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P743" t="n">
@@ -56233,7 +56233,7 @@
       </c>
       <c r="O744" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P744" t="n">
@@ -56308,7 +56308,7 @@
       </c>
       <c r="O745" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P745" t="n">
@@ -56383,7 +56383,7 @@
       </c>
       <c r="O746" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P746" t="n">
@@ -56458,7 +56458,7 @@
       </c>
       <c r="O747" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P747" t="n">
@@ -56533,7 +56533,7 @@
       </c>
       <c r="O748" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P748" t="n">
@@ -56608,7 +56608,7 @@
       </c>
       <c r="O749" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P749" t="n">
@@ -56683,7 +56683,7 @@
       </c>
       <c r="O750" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P750" t="n">
@@ -56758,7 +56758,7 @@
       </c>
       <c r="O751" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P751" t="n">
@@ -56833,7 +56833,7 @@
       </c>
       <c r="O752" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P752" t="n">
@@ -56908,7 +56908,7 @@
       </c>
       <c r="O753" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P753" t="n">
@@ -56983,7 +56983,7 @@
       </c>
       <c r="O754" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P754" t="n">
@@ -57058,7 +57058,7 @@
       </c>
       <c r="O755" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P755" t="n">
@@ -57133,7 +57133,7 @@
       </c>
       <c r="O756" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P756" t="n">
@@ -57208,7 +57208,7 @@
       </c>
       <c r="O757" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P757" t="n">
@@ -57283,7 +57283,7 @@
       </c>
       <c r="O758" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P758" t="n">
@@ -57358,7 +57358,7 @@
       </c>
       <c r="O759" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P759" t="n">
@@ -57433,7 +57433,7 @@
       </c>
       <c r="O760" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P760" t="n">
@@ -57508,7 +57508,7 @@
       </c>
       <c r="O761" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P761" t="n">
@@ -57583,7 +57583,7 @@
       </c>
       <c r="O762" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P762" t="n">
@@ -57658,7 +57658,7 @@
       </c>
       <c r="O763" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P763" t="n">
@@ -57733,7 +57733,7 @@
       </c>
       <c r="O764" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P764" t="n">
@@ -57808,7 +57808,7 @@
       </c>
       <c r="O765" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P765" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="O766" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P766" t="n">
@@ -57958,7 +57958,7 @@
       </c>
       <c r="O767" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P767" t="n">
@@ -58033,7 +58033,7 @@
       </c>
       <c r="O768" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P768" t="n">
@@ -58108,7 +58108,7 @@
       </c>
       <c r="O769" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P769" t="n">
@@ -58183,7 +58183,7 @@
       </c>
       <c r="O770" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P770" t="n">
@@ -58258,7 +58258,7 @@
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P771" t="n">
@@ -58333,7 +58333,7 @@
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P772" t="n">
@@ -58408,7 +58408,7 @@
       </c>
       <c r="O773" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P773" t="n">
@@ -58483,7 +58483,7 @@
       </c>
       <c r="O774" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P774" t="n">
@@ -58558,7 +58558,7 @@
       </c>
       <c r="O775" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P775" t="n">
@@ -58633,7 +58633,7 @@
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P776" t="n">
@@ -58708,7 +58708,7 @@
       </c>
       <c r="O777" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P777" t="n">
@@ -58783,7 +58783,7 @@
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P778" t="n">
@@ -58858,7 +58858,7 @@
       </c>
       <c r="O779" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P779" t="n">
@@ -58933,7 +58933,7 @@
       </c>
       <c r="O780" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P780" t="n">
@@ -59008,7 +59008,7 @@
       </c>
       <c r="O781" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P781" t="n">
@@ -59083,7 +59083,7 @@
       </c>
       <c r="O782" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P782" t="n">
@@ -59158,7 +59158,7 @@
       </c>
       <c r="O783" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P783" t="n">
@@ -59233,7 +59233,7 @@
       </c>
       <c r="O784" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P784" t="n">
@@ -59308,7 +59308,7 @@
       </c>
       <c r="O785" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P785" t="n">
@@ -59383,7 +59383,7 @@
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P786" t="n">
@@ -59458,7 +59458,7 @@
       </c>
       <c r="O787" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P787" t="n">
@@ -59533,7 +59533,7 @@
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P788" t="n">
@@ -59608,7 +59608,7 @@
       </c>
       <c r="O789" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P789" t="n">
@@ -59683,7 +59683,7 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P790" t="n">
@@ -59758,7 +59758,7 @@
       </c>
       <c r="O791" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P791" t="n">
@@ -59833,7 +59833,7 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P792" t="n">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="O793" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P793" t="n">
@@ -59983,7 +59983,7 @@
       </c>
       <c r="O794" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P794" t="n">
@@ -60058,7 +60058,7 @@
       </c>
       <c r="O795" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P795" t="n">
@@ -60133,7 +60133,7 @@
       </c>
       <c r="O796" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P796" t="n">
@@ -60208,7 +60208,7 @@
       </c>
       <c r="O797" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P797" t="n">
@@ -60283,7 +60283,7 @@
       </c>
       <c r="O798" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P798" t="n">
@@ -60358,7 +60358,7 @@
       </c>
       <c r="O799" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P799" t="n">
@@ -60433,7 +60433,7 @@
       </c>
       <c r="O800" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P800" t="n">
@@ -60508,7 +60508,7 @@
       </c>
       <c r="O801" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P801" t="n">
@@ -60583,7 +60583,7 @@
       </c>
       <c r="O802" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P802" t="n">
@@ -60658,7 +60658,7 @@
       </c>
       <c r="O803" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P803" t="n">
@@ -60733,7 +60733,7 @@
       </c>
       <c r="O804" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P804" t="n">
@@ -60808,7 +60808,7 @@
       </c>
       <c r="O805" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P805" t="n">
@@ -60883,7 +60883,7 @@
       </c>
       <c r="O806" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P806" t="n">
@@ -60958,7 +60958,7 @@
       </c>
       <c r="O807" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P807" t="n">
@@ -61033,7 +61033,7 @@
       </c>
       <c r="O808" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P808" t="n">
@@ -61108,7 +61108,7 @@
       </c>
       <c r="O809" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P809" t="n">
@@ -61183,7 +61183,7 @@
       </c>
       <c r="O810" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P810" t="n">
@@ -61258,7 +61258,7 @@
       </c>
       <c r="O811" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P811" t="n">
@@ -61333,7 +61333,7 @@
       </c>
       <c r="O812" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P812" t="n">
@@ -61408,7 +61408,7 @@
       </c>
       <c r="O813" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P813" t="n">
@@ -61483,7 +61483,7 @@
       </c>
       <c r="O814" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P814" t="n">
@@ -61558,7 +61558,7 @@
       </c>
       <c r="O815" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P815" t="n">
@@ -61633,7 +61633,7 @@
       </c>
       <c r="O816" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P816" t="n">
@@ -61708,7 +61708,7 @@
       </c>
       <c r="O817" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P817" t="n">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="O818" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P818" t="n">
@@ -61858,7 +61858,7 @@
       </c>
       <c r="O819" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P819" t="n">
@@ -61933,7 +61933,7 @@
       </c>
       <c r="O820" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P820" t="n">
@@ -62008,7 +62008,7 @@
       </c>
       <c r="O821" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P821" t="n">
@@ -62083,7 +62083,7 @@
       </c>
       <c r="O822" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P822" t="n">
@@ -62158,7 +62158,7 @@
       </c>
       <c r="O823" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P823" t="n">
@@ -62233,7 +62233,7 @@
       </c>
       <c r="O824" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P824" t="n">
@@ -62308,7 +62308,7 @@
       </c>
       <c r="O825" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P825" t="n">
@@ -62383,7 +62383,7 @@
       </c>
       <c r="O826" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P826" t="n">
@@ -62458,7 +62458,7 @@
       </c>
       <c r="O827" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P827" t="n">
@@ -62533,7 +62533,7 @@
       </c>
       <c r="O828" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P828" t="n">
@@ -62608,7 +62608,7 @@
       </c>
       <c r="O829" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P829" t="n">
@@ -62683,7 +62683,7 @@
       </c>
       <c r="O830" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P830" t="n">
@@ -62758,7 +62758,7 @@
       </c>
       <c r="O831" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P831" t="n">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="O832" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P832" t="n">
@@ -62908,7 +62908,7 @@
       </c>
       <c r="O833" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P833" t="n">
@@ -62983,7 +62983,7 @@
       </c>
       <c r="O834" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P834" t="n">
@@ -63058,7 +63058,7 @@
       </c>
       <c r="O835" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P835" t="n">
@@ -63133,7 +63133,7 @@
       </c>
       <c r="O836" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P836" t="n">
@@ -63208,7 +63208,7 @@
       </c>
       <c r="O837" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P837" t="n">
@@ -63283,7 +63283,7 @@
       </c>
       <c r="O838" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P838" t="n">
@@ -63358,7 +63358,7 @@
       </c>
       <c r="O839" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P839" t="n">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="O840" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P840" t="n">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="O841" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P841" t="n">
